--- a/reports/meta-llama_Llama-3.1-8B-Instruct.xlsx
+++ b/reports/meta-llama_Llama-3.1-8B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-10 23:18:38</t>
+          <t>2026-02-24 21:17:41</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9/34 (26.5%)</t>
+          <t>8/34 (23.5%)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7/13 (53.8%)</t>
+          <t>6/13 (46.2%)</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/15 (40.0%)</t>
+          <t>5/15 (33.3%)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>63/81 (77.8%)</t>
+          <t>61/81 (75.3%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9/37 (24.3%)</t>
+          <t>8/37 (21.6%)</t>
         </is>
       </c>
     </row>
@@ -5982,9 +5982,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6848,9 +6848,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7204,9 +7204,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -17574,9 +17574,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B948" s="12" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B948" s="11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -19147,9 +19147,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1109" s="12" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B1109" s="11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -19799,9 +19799,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1172" s="12" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B1172" s="11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>

--- a/reports/meta-llama_Llama-3.1-8B-Instruct.xlsx
+++ b/reports/meta-llama_Llama-3.1-8B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-24 21:17:41</t>
+          <t>2026-03-08 11:30:05</t>
         </is>
       </c>
     </row>

--- a/reports/meta-llama_Llama-3.1-8B-Instruct.xlsx
+++ b/reports/meta-llama_Llama-3.1-8B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08 13:52:33</t>
+          <t>2026-03-10 18:31:58</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16/25 (64.0%)</t>
+          <t>17/25 (68.0%)</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1/10 (10.0%)</t>
+          <t>3/10 (30.0%)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7/34 (20.6%)</t>
+          <t>10/34 (29.4%)</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26/30 (86.7%)</t>
+          <t>25/30 (83.3%)</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11/25 (44.0%)</t>
+          <t>18/25 (72.0%)</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5/15 (33.3%)</t>
+          <t>6/15 (40.0%)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>63/83 (75.9%)</t>
+          <t>66/83 (79.5%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30/74 (40.5%)</t>
+          <t>40/74 (54.1%)</t>
         </is>
       </c>
     </row>
@@ -2412,9 +2412,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2972,9 +2972,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3009,9 +3009,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3904,9 +3904,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4424,9 +4424,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4461,9 +4461,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4505,9 +4505,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4542,9 +4542,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4802,9 +4802,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4839,9 +4839,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4952,9 +4952,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6671,9 +6671,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7238,9 +7238,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7391,9 +7391,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7550,9 +7550,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7821,9 +7821,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8464,9 +8464,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E237" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -11365,9 +11365,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B283" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B283" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -12433,9 +12433,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B388" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B388" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -12510,9 +12510,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B395" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B395" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -14157,9 +14157,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B563" s="12" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B563" s="11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -15098,9 +15098,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B661" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B661" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15172,9 +15172,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B668" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B668" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15239,9 +15239,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B675" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B675" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15306,9 +15306,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B682" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B682" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15776,9 +15776,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B731" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B731" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15843,9 +15843,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B738" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B738" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -16046,9 +16046,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B759" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B759" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -19189,9 +19189,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1081" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1081" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -20221,9 +20221,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1186" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1186" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -20518,9 +20518,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1214" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1214" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -20817,9 +20817,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1242" s="12" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B1242" s="11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -21325,9 +21325,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1291" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1291" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -22478,9 +22478,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1410" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1410" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
